--- a/data_extactor/batch_10_fa/batch_0032_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0032_fa.xlsx
@@ -493,7 +493,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Anthropology and Archeology Teachers, Postsecondary (استادان انسان‌شناسی و باستان‌شناسی، پس از متوسطه)</t>
+          <t>استادان انسان‌شناسی و باستان‌شناسی، پس از متوسطه (Anthropology and Archeology Teachers, Postsecondary)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -503,12 +503,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Adobe Acrobat | Adobe Creative Cloud software | Adobe Dreamweaver | Adobe Illustrator | Adobe Photoshop | Blackboard Learn | نرم‌افزار ویرایش مشارکتی | نرم‌افزار سیستم مدیریت دوره | DOC Cop | نرم‌افزار Desire2Learn LMS | نرم‌افزار دیجیتالی‌سازی | ESRI ArcGIS Geostatistical Analyst | ESRI ArcGIS Spatial Analyst | ESRI ArcGIS software | ESRI ArcMap | ESRI ArcView | ESRI ArcView 3D Analyst | نرم‌افزار ایمیل | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | GibbsCAM | Golden Software Surfer | Google Docs | IBM SPSS Statistics | نرم‌افزار اسکن تصویر | سیستم مدیریت یادگیری LMS | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Sakai CLE | نرم‌افزار مرورگر وب | iParadigms Turnitin</t>
+          <t>Adobe Acrobat | نرم‌افزار Adobe Creative Cloud | Adobe Dreamweaver | Adobe Illustrator | Adobe Photoshop | Blackboard Learn | نرم‌افزار ویرایش مشارکتی | نرم‌افزار سیستم مدیریت دوره | DOC Cop | نرم‌افزار Desire2Learn LMS | نرم‌افزار دیجیتالی‌سازی | ESRI ArcGIS Geostatistical Analyst | ESRI ArcGIS Spatial Analyst | نرم‌افزار ESRI ArcGIS | ESRI ArcMap | ESRI ArcView | ESRI ArcView 3D Analyst | نرم‌افزار ایمیل | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | GibbsCAM | Golden Software Surfer | Google Docs | IBM SPSS Statistics | نرم‌افزار اسکن تصویر | سیستم مدیریت یادگیری LMS | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Sakai CLE | نرم‌افزار مرورگر وب | iParadigms Turnitin</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>سخنرانی | درک مطلب | نوشتن | گوش دادن فعال | راهبردهای یادگیری | یادگیری فعال | تفکر انتقادی | نظارت | علوم</t>
+          <t>سخن گفتن | درک مطلب | نگارش | گوش دادن فعال | راهبردهای یادگیری | یادگیری فعال | تفکر انتقادی | نظارت | علوم</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -518,17 +518,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>بیان شفاهی | وضوح گفتار | بیان نوشتاری | درک نوشتاری | درک شفاهی | دید نزدیک | استدلال استقرایی | استدلال قیاسی | نظم‌دهی اطلاعات | تشخیص گفتار | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | حساسیت به مسئله | اصالت | توجه انتخابی | حافظه | دید دور | اشتراک زمانی | انعطاف‌پذیری بستار</t>
+          <t>بیان شفاهی | وضوح گفتار | بیان کتبی | درک کتبی | درک شفاهی | بینایی نزدیک | استدلال استقرایی | استدلال قیاسی | ترتیب‌دهی اطلاعات | تشخیص گفتار | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | حساسیت به مسئله | اصالت | توجه انتخابی | حفظ کردن | بینایی دور | تقسیم توجه | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>ایمیل | بحث‌های رودررو با افراد و درون تیم‌ها | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | تماس با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | محیط داخلی، دارای کنترل محیطی | سخنرانی عمومی | سطح رقابت | صرف زمان برای نشستن | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | اهمیت دقیق یا صحیح بودن | نزدیکی فیزیکی</t>
+          <t>ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | محیط داخلی، دارای کنترل شرایط محیطی | سخنرانی عمومی | سطح رقابت | صرف زمان برای نشستن | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | اهمیت دقیق یا درست بودن | نزدیکی فیزیکی</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>انسان‌شناسان و باستان‌شناسان | استادان مطالعات منطقه‌ای، قومی و فرهنگی، پس از متوسطه | استادان علوم جوی، زمین، دریایی و فضایی، پس از متوسطه | استادان علوم زیستی، پس از متوسطه | استادان ارتباطات، پس از متوسطه | استادان آموزش و پرورش، پس از متوسطه | معلمان مدارس ابتدایی، به جز آموزش ویژه | استادان زبان و ادبیات انگلیسی، پس از متوسطه | استادان علوم محیطی، پس از متوسطه | استادان علوم خانواده و مصرف‌کننده، پس از متوسطه | استادان جغرافیا، پس از متوسطه | استادان تاریخ، پس از متوسطه | معلمان مدارس راهنمایی، به جز آموزش ویژه و فنی/حرفه‌ای | استادان فلسفه و دین، پس از متوسطه | استادان علوم سیاسی، پس از متوسطه | استادان روان‌شناسی، پس از متوسطه | معلمان مدارس متوسطه، به جز آموزش ویژه و فنی/حرفه‌ای | استادان مددکاری اجتماعی، پس از متوسطه | استادان جامعه‌شناسی، پس از متوسطه | دستیاران آموزشی، پس از متوسطه</t>
+          <t>مردم‌شناسان و باستان‌شناسان | استادان مطالعات منطقه‌ای، قومی و فرهنگی، پس از متوسطه | مدرسان علوم جوی، زمین، دریایی و فضایی، پس از متوسطه | مدرسان علوم زیستی، پس از متوسطه | مدرسان ارتباطات، آموزش عالی | مدرسان علوم تربیتی، آموزش عالی | معلمان دبستان، به استثنای آموزش استثنایی | مدرسان زبان و ادبیات انگلیسی، آموزش عالی | مدرسان علوم محیطی، پس از متوسطه | اساتید علوم خانواده و مصرف‌کننده، پس از متوسطه | استادان جغرافیا، پس از متوسطه | مدرسان تاریخ، آموزش عالی | معلمان دوره راهنمایی، به استثنای آموزش استثنایی و فنی/حرفه‌ای | اساتید فلسفه و دین، پس از متوسطه | استادان علوم سیاسی، پس از متوسطه | استادان روان‌شناسی، پس از متوسطه | معلمان دبیرستان، به استثنای آموزش ویژه و فنی/حرفه‌ای | مدرسان مددکاری اجتماعی، آموزش عالی | استادان جامعه‌شناسی، پس از متوسطه | دستیاران آموزشی، مقطع پس از متوسطه</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -550,7 +550,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Area, Ethnic, and Cultural Studies Teachers, Postsecondary (استادان مطالعات منطقه‌ای، قومی و فرهنگی، پس از متوسطه)</t>
+          <t>استادان مطالعات منطقه‌ای، قومی و فرهنگی، پس از متوسطه (Area, Ethnic, and Cultural Studies Teachers, Postsecondary)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -565,7 +565,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>درک مطلب | سخنرانی | راهبردهای یادگیری | یادگیری فعال | نوشتن | گوش دادن فعال | تفکر انتقادی | نظارت</t>
+          <t>درک مطلب | سخن گفتن | راهبردهای یادگیری | یادگیری فعال | نگارش | گوش دادن فعال | تفکر انتقادی | نظارت</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -575,17 +575,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>بیان شفاهی | بیان نوشتاری | وضوح گفتار | درک شفاهی | درک نوشتاری | استدلال استقرایی | دید نزدیک | استدلال قیاسی | تشخیص گفتار | حساسیت به مسئله | اصالت | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | نظم‌دهی اطلاعات</t>
+          <t>بیان شفاهی | بیان کتبی | وضوح گفتار | درک شفاهی | درک کتبی | استدلال استقرایی | بینایی نزدیک | استدلال قیاسی | تشخیص گفتار | حساسیت به مسئله | اصالت | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>ایمیل | بحث‌های رودررو با افراد و درون تیم‌ها | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | محیط داخلی، دارای کنترل محیطی | سخنرانی عمومی | تماس با دیگران | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | کار با یا مشارکت در یک گروه کاری یا تیم | سطح رقابت | فشار زمانی | صرف زمان برای نشستن | تکرار تصمیم‌گیری | نامه‌ها و یادداشت‌های کتبی | اهمیت دقیق یا صحیح بودن</t>
+          <t>ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | محیط داخلی، دارای کنترل شرایط محیطی | سخنرانی عمومی | ارتباط با دیگران | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | کار با یا مشارکت در یک گروه کاری یا تیم | سطح رقابت | فشار زمانی | صرف زمان برای نشستن | فراوانی تصمیم‌گیری | نامه‌ها و یادداشت‌های کتبی | اهمیت دقیق یا درست بودن</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>مربیان آموزش پایه بزرگسالان، آموزش متوسطه بزرگسالان و انگلیسی به عنوان زبان دوم | استادان انسان‌شناسی و باستان‌شناسی، پس از متوسطه | استادان ارتباطات، پس از متوسطه | استادان آموزش و پرورش، پس از متوسطه | معلمان مدارس ابتدایی، به جز آموزش ویژه | استادان زبان و ادبیات انگلیسی، پس از متوسطه | استادان علوم خانواده و مصرف‌کننده، پس از متوسطه | استادان زبان و ادبیات خارجی، پس از متوسطه | استادان جغرافیا، پس از متوسطه | استادان تاریخ، پس از متوسطه | استادان حقوق، پس از متوسطه | استادان علوم کتابداری، پس از متوسطه | معلمان مدارس راهنمایی، به جز آموزش ویژه و فنی/حرفه‌ای | استادان فلسفه و دین، پس از متوسطه | استادان علوم سیاسی، پس از متوسطه | استادان روان‌شناسی، پس از متوسطه | معلمان مدارس متوسطه، به جز آموزش ویژه و فنی/حرفه‌ای | استادان مددکاری اجتماعی، پس از متوسطه | استادان جامعه‌شناسی، پس از متوسطه | دستیاران آموزشی، پس از متوسطه</t>
+          <t>مربیان آموزش پایه بزرگسالان، آموزش متوسطه بزرگسالان و انگلیسی به عنوان زبان دوم | استادان انسان‌شناسی و باستان‌شناسی، پس از متوسطه | مدرسان ارتباطات، آموزش عالی | مدرسان علوم تربیتی، آموزش عالی | معلمان دبستان، به استثنای آموزش استثنایی | مدرسان زبان و ادبیات انگلیسی، آموزش عالی | اساتید علوم خانواده و مصرف‌کننده، پس از متوسطه | مدرسان زبان و ادبیات خارجی، آموزش عالی | استادان جغرافیا، پس از متوسطه | مدرسان تاریخ، آموزش عالی | مدرسان حقوق، آموزش عالی | مدرسان علوم کتابداری، آموزش عالی | معلمان دوره راهنمایی، به استثنای آموزش استثنایی و فنی/حرفه‌ای | اساتید فلسفه و دین، پس از متوسطه | استادان علوم سیاسی، پس از متوسطه | استادان روان‌شناسی، پس از متوسطه | معلمان دبیرستان، به استثنای آموزش ویژه و فنی/حرفه‌ای | مدرسان مددکاری اجتماعی، آموزش عالی | استادان جامعه‌شناسی، پس از متوسطه | دستیاران آموزشی، مقطع پس از متوسطه</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Economics Teachers, Postsecondary (استادان اقتصاد، پس از متوسطه)</t>
+          <t>استادان اقتصاد، پس از متوسطه (Economics Teachers, Postsecondary)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -617,12 +617,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Aptech Systems GAUSS | Blackboard Learn | نرم‌افزار ویرایش مشارکتی | نرم‌افزار سیستم مدیریت دوره | DOC Cop | نرم‌افزار Desire2Learn LMS | نرم‌افزار اقتصادسنجی LIMDEP | Econport | نرم‌افزار ایمیل | Estima RATS | FEAR | Facebook | Gnuplot | Google Docs | نرم‌افزار اسکن تصویر | Insightful S-PLUS | نرم‌افزار شبیه‌ساز سهام JessX | سیستم مدیریت یادگیری LMS | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Minitab | Moodle | Python | Python Experimental Economics Toolkit PEET | R | Sakai CLE | StataCorp Stata | Sun Microsystems Java | The MathWorks MATLAB | نرم‌افزار مدل‌سازی سری زمانی TSM | نرم‌افزار مرورگر وب | Zocalo | iParadigms Turnitin | z-Tree</t>
+          <t>Aptech Systems GAUSS | Blackboard Learn | نرم‌افزار ویرایش مشارکتی | نرم‌افزار سیستم مدیریت دوره | DOC Cop | نرم‌افزار Desire2Learn LMS | Econometric Software LIMDEP | Econport | نرم‌افزار ایمیل | Estima RATS | FEAR | Facebook | Gnuplot | Google Docs | نرم‌افزار اسکن تصویر | Insightful S-PLUS | نرم‌افزار شبیه‌ساز سهام JessX | سیستم مدیریت یادگیری LMS | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Minitab | Moodle | Python | Python Experimental Economics Toolkit PEET | R | Sakai CLE | StataCorp Stata | Sun Microsystems Java | The MathWorks MATLAB | نرم‌افزار مدل‌سازی سری زمانی TSM | نرم‌افزار مرورگر وب | Zocalo | iParadigms Turnitin | z-Tree</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>سخنرانی | گوش دادن فعال | درک مطلب | نوشتن | تفکر انتقادی | راهبردهای یادگیری | یادگیری فعال | ریاضیات | نظارت</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | نگارش | تفکر انتقادی | راهبردهای یادگیری | یادگیری فعال | ریاضیات | نظارت</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -632,17 +632,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>بیان شفاهی | وضوح گفتار | درک شفاهی | درک نوشتاری | بیان نوشتاری | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | دید نزدیک | حساسیت به مسئله | استدلال ریاضی | توانایی عددی | نظم‌دهی اطلاعات | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | اصالت | حافظه</t>
+          <t>بیان شفاهی | وضوح گفتار | درک شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | بینایی نزدیک | حساسیت به مسئله | استدلال ریاضی | توانایی عددی | ترتیب‌دهی اطلاعات | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | اصالت | حفظ کردن</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>ایمیل | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | بحث‌های رودررو با افراد و درون تیم‌ها | صرف زمان برای نشستن | تماس با دیگران | سخنرانی عمومی | محیط داخلی، دارای کنترل محیطی | اهمیت دقیق یا صحیح بودن | سطح رقابت</t>
+          <t>ایمیل | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای نشستن | ارتباط با دیگران | سخنرانی عمومی | محیط داخلی، دارای کنترل شرایط محیطی | اهمیت دقیق یا درست بودن | سطح رقابت</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>استادان علوم کشاورزی، پس از متوسطه | استادان انسان‌شناسی و باستان‌شناسی، پس از متوسطه | استادان مطالعات منطقه‌ای، قومی و فرهنگی، پس از متوسطه | استادان کسب‌وکار، پس از متوسطه | معلمان آموزش فنی/حرفه‌ای، مدارس راهنمایی | اقتصاددانان | مدیران آموزشی، پس از متوسطه | استادان آموزش و پرورش، پس از متوسطه | اقتصاددانان محیط زیست | استادان علوم محیطی، پس از متوسطه | استادان علوم خانواده و مصرف‌کننده، پس از متوسطه | استادان جنگلداری و علوم حفاظتی، پس از متوسطه | استادان جغرافیا، پس از متوسطه | استادان حقوق، پس از متوسطه | استادان علوم ریاضی، پس از متوسطه | استادان علوم سیاسی، پس از متوسطه | استادان روان‌شناسی، پس از متوسطه | استادان مددکاری اجتماعی، پس از متوسطه | استادان جامعه‌شناسی، پس از متوسطه | دستیاران آموزشی، پس از متوسطه</t>
+          <t>مدرسان علوم کشاورزی، پس از متوسطه | استادان انسان‌شناسی و باستان‌شناسی، پس از متوسطه | استادان مطالعات منطقه‌ای، قومی و فرهنگی، پس از متوسطه | اساتید کسب‌وکار، پس از متوسطه | معلمان آموزش‌های شغلی/فنی، دوره راهنمایی | اقتصاددانان | مدیران آموزشی، پس از متوسطه | مدرسان علوم تربیتی، آموزش عالی | اقتصاددانان محیط‌زیست | مدرسان علوم محیطی، پس از متوسطه | اساتید علوم خانواده و مصرف‌کننده، پس از متوسطه | مدرسان علوم جنگلداری و حفاظت، پس از متوسطه | استادان جغرافیا، پس از متوسطه | مدرسان حقوق، آموزش عالی | مدرسان علوم ریاضی، پس از متوسطه | استادان علوم سیاسی، پس از متوسطه | استادان روان‌شناسی، پس از متوسطه | مدرسان مددکاری اجتماعی، آموزش عالی | استادان جامعه‌شناسی، پس از متوسطه | دستیاران آموزشی، مقطع پس از متوسطه</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Geography Teachers, Postsecondary (استادان جغرافیا، پس از متوسطه)</t>
+          <t>استادان جغرافیا، پس از متوسطه (Geography Teachers, Postsecondary)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Adobe Acrobat Reader | Adobe Creative Cloud software | Blackboard Learn | Caliper Maptitude | Clark Labs CartaLinx | Clark Labs IDRISI | نرم‌افزار ویرایش مشارکتی | نرم‌افزار سیستم مدیریت دوره | DOC Cop | نرم‌افزار Desire2Learn LMS | ESRI ArcGIS Geostatistical Analyst | ESRI ArcGIS software | ESRI ArcView | ESRI ArcView 3D Analyst | نرم‌افزار ایمیل | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | سیستم‌های سیستم اطلاعات جغرافیایی GIS | سیستم پشتیبانی تحلیل منابع جغرافیایی GRASS | Google Docs | HEC-RAS | IBM SPSS Statistics | ITT Exelis Visual Information Solutions ENVI | نرم‌افزار اسکن تصویر | Insightful S-PLUS | زبان تعریف رابط IDL | سیستم مدیریت یادگیری LMS | Leica Geosystems ERDAS IMAGINE | Microsoft Excel | Microsoft Internet Explorer | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Publisher | Microsoft Word | Mozilla Firefox | Sakai CLE | The MathWorks MATLAB | Tibco S-PLUS | نرم‌افزار مرورگر وب | iParadigms Turnitin</t>
+          <t>Adobe Acrobat Reader | نرم‌افزار Adobe Creative Cloud | Blackboard Learn | Caliper Maptitude | Clark Labs CartaLinx | Clark Labs IDRISI | نرم‌افزار ویرایش مشارکتی | نرم‌افزار سیستم مدیریت دوره | DOC Cop | نرم‌افزار Desire2Learn LMS | ESRI ArcGIS Geostatistical Analyst | نرم‌افزار ESRI ArcGIS | ESRI ArcView | ESRI ArcView 3D Analyst | نرم‌افزار ایمیل | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | سیستم‌های سیستم اطلاعات جغرافیایی GIS | سیستم پشتیبانی تحلیل منابع جغرافیایی GRASS | Google Docs | HEC-RAS | IBM SPSS Statistics | ITT Exelis Visual Information Solutions ENVI | نرم‌افزار اسکن تصویر | Insightful S-PLUS | زبان تعریف رابط IDL | سیستم مدیریت یادگیری LMS | Leica Geosystems ERDAS IMAGINE | Microsoft Excel | Microsoft Internet Explorer | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Publisher | Microsoft Word | Mozilla Firefox | Sakai CLE | The MathWorks MATLAB | Tibco S-PLUS | نرم‌افزار مرورگر وب | iParadigms Turnitin</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>نوشتن | سخنرانی | گوش دادن فعال | درک مطلب | تفکر انتقادی | یادگیری فعال | راهبردهای یادگیری | علوم | نظارت</t>
+          <t>نگارش | سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | یادگیری فعال | راهبردهای یادگیری | علوم | نظارت</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -689,17 +689,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>بیان شفاهی | بیان نوشتاری | درک شفاهی | درک نوشتاری | وضوح گفتار | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | حساسیت به مسئله | دید نزدیک | نظم‌دهی اطلاعات | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | اصالت</t>
+          <t>بیان شفاهی | بیان کتبی | درک شفاهی | درک کتبی | وضوح گفتار | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | حساسیت به مسئله | بینایی نزدیک | ترتیب‌دهی اطلاعات | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | اصالت</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>ایمیل | آزادی در تصمیم‌گیری | بحث‌های رودررو با افراد و درون تیم‌ها | تعیین وظایف، اولویت‌ها و اهداف | محیط داخلی، دارای کنترل محیطی | سخنرانی عمومی | تماس با دیگران | اهمیت دقیق یا صحیح بودن | صرف زمان برای نشستن | کار با یا مشارکت در یک گروه کاری یا تیم | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | سطح رقابت | فشار زمانی</t>
+          <t>ایمیل | آزادی در تصمیم‌گیری | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تعیین وظایف، اولویت‌ها و اهداف | محیط داخلی، دارای کنترل شرایط محیطی | سخنرانی عمومی | ارتباط با دیگران | اهمیت دقیق یا درست بودن | صرف زمان برای نشستن | کار با یا مشارکت در یک گروه کاری یا تیم | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | سطح رقابت | فشار زمانی</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>مربیان آموزش پایه بزرگسالان، آموزش متوسطه بزرگسالان و انگلیسی به عنوان زبان دوم | استادان انسان‌شناسی و باستان‌شناسی، پس از متوسطه | استادان مطالعات منطقه‌ای، قومی و فرهنگی، پس از متوسطه | استادان علوم جوی، زمین، دریایی و فضایی، پس از متوسطه | استادان علوم زیستی، پس از متوسطه | استادان اقتصاد، پس از متوسطه | استادان آموزش و پرورش، پس از متوسطه | معلمان مدارس ابتدایی، به جز آموزش ویژه | استادان علوم محیطی، پس از متوسطه | استادان جنگلداری و علوم حفاظتی، پس از متوسطه | جغرافی‌دانان | استادان تاریخ، پس از متوسطه | استادان علوم کتابداری، پس از متوسطه | استادان علوم ریاضی، پس از متوسطه | معلمان مدارس راهنمایی، به جز آموزش ویژه و فنی/حرفه‌ای | استادان علوم سیاسی، پس از متوسطه | معلمان مدارس متوسطه، به جز آموزش ویژه و فنی/حرفه‌ای | استادان جامعه‌شناسی، پس از متوسطه | معلمان آموزش ویژه، مدارس ابتدایی | دستیاران آموزشی، پس از متوسطه</t>
+          <t>مربیان آموزش پایه بزرگسالان، آموزش متوسطه بزرگسالان و انگلیسی به عنوان زبان دوم | استادان انسان‌شناسی و باستان‌شناسی، پس از متوسطه | استادان مطالعات منطقه‌ای، قومی و فرهنگی، پس از متوسطه | مدرسان علوم جوی، زمین، دریایی و فضایی، پس از متوسطه | مدرسان علوم زیستی، پس از متوسطه | استادان اقتصاد، پس از متوسطه | مدرسان علوم تربیتی، آموزش عالی | معلمان دبستان، به استثنای آموزش استثنایی | مدرسان علوم محیطی، پس از متوسطه | مدرسان علوم جنگلداری و حفاظت، پس از متوسطه | جغرافیدانان | مدرسان تاریخ، آموزش عالی | مدرسان علوم کتابداری، آموزش عالی | مدرسان علوم ریاضی، پس از متوسطه | معلمان دوره راهنمایی، به استثنای آموزش استثنایی و فنی/حرفه‌ای | استادان علوم سیاسی، پس از متوسطه | معلمان دبیرستان، به استثنای آموزش ویژه و فنی/حرفه‌ای | استادان جامعه‌شناسی، پس از متوسطه | معلمان آموزش ویژه، دبستان | دستیاران آموزشی، مقطع پس از متوسطه</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -721,7 +721,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Political Science Teachers, Postsecondary (استادان علوم سیاسی، پس از متوسطه)</t>
+          <t>استادان علوم سیاسی، پس از متوسطه (Political Science Teachers, Postsecondary)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -731,32 +731,32 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Blackboard Learn | C | نرم‌افزار ویرایش مشارکتی | ContextMiner | نرم‌افزار سیستم مدیریت دوره | DOC Cop | نرم‌افزار Desire2Learn LMS | نرم‌افزار ایمیل | Empirisoft MediaLab | زبان برنامه‌نویسی FORTRAN | Google Docs | نرم‌افزار اسکن تصویر | سیستم مدیریت یادگیری LMS | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Moodle | R | Sakai CLE | W-NOMINATE | نرم‌افزار مرورگر وب | WinBUGS | iParadigms Turnitin | poLCA | z-Tree</t>
+          <t>Blackboard Learn | C | نرم‌افزار ویرایش مشارکتی | ContextMiner | نرم‌افزار سیستم مدیریت دوره | DOC Cop | نرم‌افزار Desire2Learn LMS | نرم‌افزار ایمیل | Empirisoft MediaLab | Formula translation/translator FORTRAN | Google Docs | نرم‌افزار اسکن تصویر | سیستم مدیریت یادگیری LMS | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Moodle | R | Sakai CLE | W-NOMINATE | نرم‌افزار مرورگر وب | WinBUGS | iParadigms Turnitin | poLCA | z-Tree</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>سخنرانی | درک مطلب | یادگیری فعال | نوشتن | گوش دادن فعال | تفکر انتقادی | راهبردهای یادگیری | نظارت</t>
+          <t>سخن گفتن | درک مطلب | یادگیری فعال | نگارش | گوش دادن فعال | تفکر انتقادی | راهبردهای یادگیری | نظارت</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | حقوق و دولت | آموزش و پرورش | تاریخ و باستان‌شناسی | جامعه‌شناسی و انسان‌شناسی | جغرافیا | فلسفه و الهیات</t>
+          <t>زبان انگلیسی | قانون و دولت | آموزش و پرورش | تاریخ و باستان‌شناسی | جامعه‌شناسی و انسان‌شناسی | جغرافیا | فلسفه و الهیات</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک نوشتاری | درک شفاهی | بیان شفاهی | بیان نوشتاری | وضوح گفتار | استدلال استقرایی | دید نزدیک | تشخیص گفتار | استدلال قیاسی | حساسیت به مسئله | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | نظم‌دهی اطلاعات | اصالت | روانی ایده‌ها</t>
+          <t>درک کتبی | درک شفاهی | بیان شفاهی | بیان کتبی | وضوح گفتار | استدلال استقرایی | بینایی نزدیک | تشخیص گفتار | استدلال قیاسی | حساسیت به مسئله | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | اصالت | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>ایمیل | آزادی در تصمیم‌گیری | محیط داخلی، دارای کنترل محیطی | تعیین وظایف، اولویت‌ها و اهداف | بحث‌های رودررو با افراد و درون تیم‌ها | سخنرانی عمومی | تکرار تصمیم‌گیری | تماس با دیگران | صرف زمان برای نشستن | مکالمات تلفنی | سطح رقابت | اهمیت دقیق یا صحیح بودن | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | برخورد با مشتریان خارجی یا عموم مردم</t>
+          <t>ایمیل | آزادی در تصمیم‌گیری | محیط داخلی، دارای کنترل شرایط محیطی | تعیین وظایف، اولویت‌ها و اهداف | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | سخنرانی عمومی | فراوانی تصمیم‌گیری | ارتباط با دیگران | صرف زمان برای نشستن | مکالمات تلفنی | سطح رقابت | اهمیت دقیق یا درست بودن | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | تعامل با مشتریان خارجی یا عموم مردم</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>استادان انسان‌شناسی و باستان‌شناسی، پس از متوسطه | استادان مطالعات منطقه‌ای، قومی و فرهنگی، پس از متوسطه | استادان کسب‌وکار، پس از متوسطه | استادان ارتباطات، پس از متوسطه | استادان عدالت کیفری و اجرای قانون، پس از متوسطه | استادان اقتصاد، پس از متوسطه | استادان آموزش و پرورش، پس از متوسطه | استادان زبان و ادبیات انگلیسی، پس از متوسطه | استادان علوم خانواده و مصرف‌کننده، پس از متوسطه | استادان جغرافیا، پس از متوسطه | استادان تاریخ، پس از متوسطه | استادان حقوق، پس از متوسطه | استادان علوم کتابداری، پس از متوسطه | استادان فلسفه و دین، پس از متوسطه | دانشمندان علوم سیاسی | استادان روان‌شناسی، پس از متوسطه | استادان مددکاری اجتماعی، پس از متوسطه | جامعه‌شناسان | استادان جامعه‌شناسی، پس از متوسطه | معلمان آموزش ویژه، مدارس ابتدایی</t>
+          <t>استادان انسان‌شناسی و باستان‌شناسی، پس از متوسطه | استادان مطالعات منطقه‌ای، قومی و فرهنگی، پس از متوسطه | اساتید کسب‌وکار، پس از متوسطه | مدرسان ارتباطات، آموزش عالی | مدرسان عدالت کیفری و اجرای قانون، آموزش عالی | استادان اقتصاد، پس از متوسطه | مدرسان علوم تربیتی، آموزش عالی | مدرسان زبان و ادبیات انگلیسی، آموزش عالی | اساتید علوم خانواده و مصرف‌کننده، پس از متوسطه | استادان جغرافیا، پس از متوسطه | مدرسان تاریخ، آموزش عالی | مدرسان حقوق، آموزش عالی | مدرسان علوم کتابداری، آموزش عالی | اساتید فلسفه و دین، پس از متوسطه | دانشمندان علوم سیاسی | استادان روان‌شناسی، پس از متوسطه | مدرسان مددکاری اجتماعی، آموزش عالی | جامعه‌شناسان | استادان جامعه‌شناسی، پس از متوسطه | معلمان آموزش ویژه، دبستان</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Psychology Teachers, Postsecondary (استادان روان‌شناسی، پس از متوسطه)</t>
+          <t>استادان روان‌شناسی، پس از متوسطه (Psychology Teachers, Postsecondary)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>راهبردهای یادگیری | درک مطلب | سخنرانی | نوشتن | گوش دادن فعال | تفکر انتقادی | یادگیری فعال | نظارت | علوم | ریاضیات</t>
+          <t>راهبردهای یادگیری | درک مطلب | سخن گفتن | نگارش | گوش دادن فعال | تفکر انتقادی | یادگیری فعال | نظارت | علوم | ریاضیات</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -803,17 +803,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>بیان شفاهی | بیان نوشتاری | درک نوشتاری | وضوح گفتار | درک شفاهی | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | حساسیت به مسئله | دید نزدیک | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | نظم‌دهی اطلاعات | اصالت</t>
+          <t>بیان شفاهی | بیان کتبی | درک کتبی | وضوح گفتار | درک شفاهی | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | حساسیت به مسئله | بینایی نزدیک | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | اصالت</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>بحث‌های رودررو با افراد و درون تیم‌ها | آزادی در تصمیم‌گیری | ایمیل | محیط داخلی، دارای کنترل محیطی | تعیین وظایف، اولویت‌ها و اهداف | تماس با دیگران | سخنرانی عمومی | صرف زمان برای نشستن | کار با یا مشارکت در یک گروه کاری یا تیم | نامه‌ها و یادداشت‌های کتبی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت دقیق یا صحیح بودن</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | آزادی در تصمیم‌گیری | ایمیل | محیط داخلی، دارای کنترل شرایط محیطی | تعیین وظایف، اولویت‌ها و اهداف | ارتباط با دیگران | سخنرانی عمومی | صرف زمان برای نشستن | کار با یا مشارکت در یک گروه کاری یا تیم | نامه‌ها و یادداشت‌های کتبی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت دقیق یا درست بودن</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>استادان انسان‌شناسی و باستان‌شناسی، پس از متوسطه | استادان علوم زیستی، پس از متوسطه | استادان اقتصاد، پس از متوسطه | استادان آموزش و پرورش، پس از متوسطه | معلمان مدارس ابتدایی، به جز آموزش ویژه | استادان علوم خانواده و مصرف‌کننده، پس از متوسطه | استادان تخصص‌های بهداشتی، پس از متوسطه | استادان علوم ریاضی، پس از متوسطه | معلمان مدارس راهنمایی، به جز آموزش ویژه و فنی/حرفه‌ای | مربیان و استادان پرستاری، پس از متوسطه | استادان فلسفه و دین، پس از متوسطه | استادان مطالعات تفریحی و تناسب اندام، پس از متوسطه | روان‌شناسان مدرسه | معلمان مدارس متوسطه، به جز آموزش ویژه و فنی/حرفه‌ای | استادان مددکاری اجتماعی، پس از متوسطه | استادان جامعه‌شناسی، پس از متوسطه | معلمان آموزش ویژه، مدارس ابتدایی | معلمان آموزش ویژه، مهدکودک | دستیاران آموزشی، پس از متوسطه | معلمان خصوصی</t>
+          <t>استادان انسان‌شناسی و باستان‌شناسی، پس از متوسطه | مدرسان علوم زیستی، پس از متوسطه | استادان اقتصاد، پس از متوسطه | مدرسان علوم تربیتی، آموزش عالی | معلمان دبستان، به استثنای آموزش استثنایی | اساتید علوم خانواده و مصرف‌کننده، پس از متوسطه | استادان تخصص‌های بهداشتی، پس از متوسطه | مدرسان علوم ریاضی، پس از متوسطه | معلمان دوره راهنمایی، به استثنای آموزش استثنایی و فنی/حرفه‌ای | مربیان و استادان پرستاری، پس از متوسطه | اساتید فلسفه و دین، پس از متوسطه | اساتید مطالعات تفریحی و تناسب اندام، پس از متوسطه | روان‌شناسان مدرسه | معلمان دبیرستان، به استثنای آموزش ویژه و فنی/حرفه‌ای | مدرسان مددکاری اجتماعی، آموزش عالی | استادان جامعه‌شناسی، پس از متوسطه | معلمان آموزش ویژه، دبستان | معلمان آموزش ویژه، کودکستان | دستیاران آموزشی، مقطع پس از متوسطه | معلمان خصوصی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -835,7 +835,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sociology Teachers, Postsecondary (استادان جامعه‌شناسی، پس از متوسطه)</t>
+          <t>استادان جامعه‌شناسی، پس از متوسطه (Sociology Teachers, Postsecondary)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -845,32 +845,32 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Blackboard Learn | نرم‌افزار Blackboard | مرکز مدل‌سازی چندسطحی MLwiN | نرم‌افزار ویرایش مشارکتی | نرم‌افزار سیستم مدیریت دوره | DOC Cop | نرم‌افزار Desire2Learn LMS | نرم‌افزار اقتصادسنجی LIMDEP | نرم‌افزار ایمیل | Google Docs | IBM SPSS Statistics | نرم‌افزار اسکن تصویر | سیستم مدیریت یادگیری LMS | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Muthen &amp; Muthen Mplus | R | SAS | Sakai CLE | Scientific Software International HLM | نرم‌افزار تحلیل شبکه اجتماعی | StataCorp Stata | The MathWorks MATLAB | نرم‌افزار مرورگر وب | iParadigms Turnitin</t>
+          <t>Blackboard Learn | نرم‌افزار Blackboard | مرکز مدل‌سازی چندسطحی MLwiN | نرم‌افزار ویرایش مشارکتی | نرم‌افزار سیستم مدیریت دوره | DOC Cop | نرم‌افزار Desire2Learn LMS | Econometric Software LIMDEP | نرم‌افزار ایمیل | Google Docs | IBM SPSS Statistics | نرم‌افزار اسکن تصویر | سیستم مدیریت یادگیری LMS | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Muthen &amp; Muthen Mplus | R | SAS | Sakai CLE | Scientific Software International HLM | نرم‌افزار تحلیل شبکه اجتماعی | StataCorp Stata | The MathWorks MATLAB | نرم‌افزار مرورگر وب | iParadigms Turnitin</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>سخنرانی | راهبردهای یادگیری | نوشتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | نظارت | یادگیری فعال</t>
+          <t>سخن گفتن | راهبردهای یادگیری | نگارش | گوش دادن فعال | درک مطلب | تفکر انتقادی | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | جامعه‌شناسی و انسان‌شناسی | آموزش و پرورش | رایانه و الکترونیک | تاریخ و باستان‌شناسی | روان‌شناسی | فلسفه و الهیات | حقوق و دولت | ریاضیات | ارتباطات و رسانه | خدمات مشتری و شخصی | اداری | جغرافیا</t>
+          <t>زبان انگلیسی | جامعه‌شناسی و انسان‌شناسی | آموزش و پرورش | رایانه و الکترونیک | تاریخ و باستان‌شناسی | روان‌شناسی | فلسفه و الهیات | قانون و دولت | ریاضیات | ارتباطات و رسانه | خدمات مشتری و شخصی | اداری | جغرافیا</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | درک نوشتاری | بیان نوشتاری | استدلال استقرایی | وضوح گفتار | استدلال قیاسی | دید نزدیک | تشخیص گفتار | نظم‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | حساسیت به مسئله | اصالت</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | استدلال استقرایی | وضوح گفتار | استدلال قیاسی | بینایی نزدیک | تشخیص گفتار | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | حساسیت به مسئله | اصالت</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>ایمیل | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | محیط داخلی، دارای کنترل محیطی | بحث‌های رودررو با افراد و درون تیم‌ها | تماس با دیگران | سخنرانی عمومی | صرف زمان برای نشستن | سطح رقابت | اهمیت دقیق یا صحیح بودن | فشار زمانی | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | نامه‌ها و یادداشت‌های کتبی | تکرار تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم</t>
+          <t>ایمیل | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | محیط داخلی، دارای کنترل شرایط محیطی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | سخنرانی عمومی | صرف زمان برای نشستن | سطح رقابت | اهمیت دقیق یا درست بودن | فشار زمانی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | نامه‌ها و یادداشت‌های کتبی | فراوانی تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>استادان انسان‌شناسی و باستان‌شناسی، پس از متوسطه | استادان مطالعات منطقه‌ای، قومی و فرهنگی، پس از متوسطه | استادان ارتباطات، پس از متوسطه | استادان عدالت کیفری و اجرای قانون، پس از متوسطه | استادان اقتصاد، پس از متوسطه | استادان آموزش و پرورش، پس از متوسطه | استادان زبان و ادبیات انگلیسی، پس از متوسطه | استادان علوم خانواده و مصرف‌کننده، پس از متوسطه | استادان جغرافیا، پس از متوسطه | استادان تاریخ، پس از متوسطه | استادان حقوق، پس از متوسطه | استادان علوم کتابداری، پس از متوسطه | معلمان مدارس راهنمایی، به جز آموزش ویژه و فنی/حرفه‌ای | استادان فلسفه و دین، پس از متوسطه | استادان علوم سیاسی، پس از متوسطه | استادان روان‌شناسی، پس از متوسطه | معلمان مدارس متوسطه، به جز آموزش ویژه و فنی/حرفه‌ای | استادان مددکاری اجتماعی، پس از متوسطه | جامعه‌شناسان | دستیاران آموزشی، پس از متوسطه</t>
+          <t>استادان انسان‌شناسی و باستان‌شناسی، پس از متوسطه | استادان مطالعات منطقه‌ای، قومی و فرهنگی، پس از متوسطه | مدرسان ارتباطات، آموزش عالی | مدرسان عدالت کیفری و اجرای قانون، آموزش عالی | استادان اقتصاد، پس از متوسطه | مدرسان علوم تربیتی، آموزش عالی | مدرسان زبان و ادبیات انگلیسی، آموزش عالی | اساتید علوم خانواده و مصرف‌کننده، پس از متوسطه | استادان جغرافیا، پس از متوسطه | مدرسان تاریخ، آموزش عالی | مدرسان حقوق، آموزش عالی | مدرسان علوم کتابداری، آموزش عالی | معلمان دوره راهنمایی، به استثنای آموزش استثنایی و فنی/حرفه‌ای | اساتید فلسفه و دین، پس از متوسطه | استادان علوم سیاسی، پس از متوسطه | استادان روان‌شناسی، پس از متوسطه | معلمان دبیرستان، به استثنای آموزش ویژه و فنی/حرفه‌ای | مدرسان مددکاری اجتماعی، آموزش عالی | جامعه‌شناسان | دستیاران آموزشی، مقطع پس از متوسطه</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Social Sciences Teachers, Postsecondary, All Other (استادان علوم اجتماعی، پس از متوسطه، سایر موارد)</t>
+          <t>استادان علوم اجتماعی، پس از متوسطه، سایر موارد (Social Sciences Teachers, Postsecondary, All Other)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -907,27 +907,27 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>سخنرانی | گوش دادن فعال | درک مطلب | تفکر انتقادی | راهبردهای یادگیری | نوشتن | یادگیری فعال | نظارت</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | راهبردهای یادگیری | نگارش | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>جامعه‌شناسی و انسان‌شناسی | زبان انگلیسی | آموزش و پرورش | تاریخ و باستان‌شناسی | روان‌شناسی | حقوق و دولت | فلسفه و الهیات | ارتباطات و رسانه | رایانه و الکترونیک</t>
+          <t>جامعه‌شناسی و انسان‌شناسی | زبان انگلیسی | آموزش و پرورش | تاریخ و باستان‌شناسی | روان‌شناسی | قانون و دولت | فلسفه و الهیات | ارتباطات و رسانه | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک نوشتاری | بیان شفاهی | بیان نوشتاری | استدلال قیاسی | استدلال استقرایی | نظم‌دهی اطلاعات | حساسیت به مسئله | دید نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | توجه انتخابی | اشتراک زمانی | تجسم | حافظه</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | توجه انتخابی | تقسیم توجه | تجسم | حفظ کردن</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>بحث‌های رودررو با افراد و درون تیم‌ها | سخنرانی عمومی | تماس با دیگران | محیط داخلی، دارای کنترل محیطی | برخورد با مشتریان خارجی یا عموم مردم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم | ایمیل | مکالمات تلفنی | صرف زمان برای ایستادن | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | موقعیت‌های تعارض | تکرار تصمیم‌گیری</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | سخنرانی عمومی | ارتباط با دیگران | محیط داخلی، دارای کنترل شرایط محیطی | تعامل با مشتریان خارجی یا عموم مردم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم | ایمیل | مکالمات تلفنی | صرف زمان برای ایستادن | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | موقعیت‌های تعارض | فراوانی تصمیم‌گیری</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>استادان جامعه‌شناسی، پس از متوسطه | استادان علوم سیاسی، پس از متوسطه | استادان روان‌شناسی، پس از متوسطه | استادان اقتصاد، پس از متوسطه | استادان جغرافیا، پس از متوسطه | استادان انسان‌شناسی و باستان‌شناسی، پس از متوسطه | استادان مطالعات منطقه‌ای، قومی و فرهنگی، پس از متوسطه | استادان تاریخ، پس از متوسطه | استادان فلسفه و دین، پس از متوسطه | استادان مددکاری اجتماعی، پس از متوسطه | استادان عدالت کیفری و اجرای قانون، پس از متوسطه | استادان آموزش و پرورش، پس از متوسطه | استادان ارتباطات، پس از متوسطه | استادان کسب‌وکار، پس از متوسطه | استادان حقوق، پس از متوسطه | استادان پس از متوسطه، سایر موارد | جامعه‌شناسان | دانشمندان علوم سیاسی | مدیران آموزشی، پس از متوسطه | هماهنگ‌کنندگان آموزشی</t>
+          <t>استادان جامعه‌شناسی، پس از متوسطه | استادان علوم سیاسی، پس از متوسطه | استادان روان‌شناسی، پس از متوسطه | استادان اقتصاد، پس از متوسطه | استادان جغرافیا، پس از متوسطه | استادان انسان‌شناسی و باستان‌شناسی، پس از متوسطه | استادان مطالعات منطقه‌ای، قومی و فرهنگی، پس از متوسطه | مدرسان تاریخ، آموزش عالی | اساتید فلسفه و دین، پس از متوسطه | مدرسان مددکاری اجتماعی، آموزش عالی | مدرسان عدالت کیفری و اجرای قانون، آموزش عالی | مدرسان علوم تربیتی، آموزش عالی | مدرسان ارتباطات، آموزش عالی | اساتید کسب‌وکار، پس از متوسطه | مدرسان حقوق، آموزش عالی | اساتید پس از متوسطه، سایر موارد | جامعه‌شناسان | دانشمندان علوم سیاسی | مدیران آموزشی، پس از متوسطه | هماهنگ‌کنندگان آموزشی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Health Specialties Teachers, Postsecondary (استادان تخصص‌های بهداشتی، پس از متوسطه)</t>
+          <t>استادان تخصص‌های بهداشتی، پس از متوسطه (Health Specialties Teachers, Postsecondary)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -959,32 +959,32 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Adobe Presenter | Articulate Rapid E-Learning Studio | Blackboard Learn | نرم‌افزار Blackboard | نرم‌افزار ویرایش مشارکتی | نرم‌افزار سیستم مدیریت دوره | DOC Cop | نرم‌افزار دندانپزشکی | نرم‌افزار Desire2Learn LMS | EcoLogic ADAM Indoor Air Quality and Analytical Data Management | نرم‌افزار پرونده الکترونیک سلامت EHR | نرم‌افزار ایمیل | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | Google Docs | سیستم کدگذاری رویه‌های رایج مراقبت‌های بهداشتی HCPCS | IBM SPSS Statistics | نرم‌افزار اسکن تصویر | InteractElsevier Netter's 3D Interactive Anatomy | سیستم مدیریت یادگیری LMS | نرم‌افزار برگه داده‌های ایمنی مواد MSDS | نرم‌افزار کدگذاری وضعیت پزشکی | نرم‌افزار کدگذاری رویه‌های پزشکی | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | SAS | Sakai CLE | TechSmith Snagit | Turning Technologies TurningPoint | نرم‌افزار مرورگر وب | iParadigms Turnitin</t>
+          <t>Adobe Presenter | Articulate Rapid E-Learning Studio | Blackboard Learn | نرم‌افزار Blackboard | نرم‌افزار ویرایش مشارکتی | نرم‌افزار سیستم مدیریت دوره | DOC Cop | نرم‌افزار دندانپزشکی | نرم‌افزار Desire2Learn LMS | مدیریت داده‌های تحلیلی و کیفیت هوای داخلی EcoLogic ADAM | نرم‌افزار پرونده الکترونیک سلامت EHR | نرم‌افزار ایمیل | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | Google Docs | سیستم کدگذاری رویه‌های رایج مراقبت‌های بهداشتی HCPCS | IBM SPSS Statistics | نرم‌افزار اسکن تصویر | InteractElsevier Netter's 3D Interactive Anatomy | سیستم مدیریت یادگیری LMS | نرم‌افزار برگه اطلاعات ایمنی مواد MSDS | نرم‌افزار کدگذاری شرایط پزشکی | نرم‌افزار کدگذاری رویه‌های پزشکی | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | SAS | Sakai CLE | TechSmith Snagit | Turning Technologies TurningPoint | نرم‌افزار مرورگر وب | iParadigms Turnitin</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>درک مطلب | سخنرانی | نوشتن | گوش دادن فعال | راهبردهای یادگیری | یادگیری فعال | تفکر انتقادی | نظارت | علوم | ریاضیات</t>
+          <t>درک مطلب | سخن گفتن | نگارش | گوش دادن فعال | راهبردهای یادگیری | یادگیری فعال | تفکر انتقادی | نظارت | علوم | ریاضیات</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>آموزش و پرورش | زبان انگلیسی | زیست‌شناسی | پزشکی و دندانپزشکی | روان‌شناسی | اداری | رایانه و الکترونیک | مدیریت و اداره | ایمنی و امنیت عمومی | خدمات مشتری و شخصی | پرسنل و منابع انسانی | درمان و مشاوره | ریاضیات | ارتباطات و رسانه | شیمی | حقوق و دولت</t>
+          <t>آموزش و پرورش | زبان انگلیسی | زیست‌شناسی | پزشکی و دندان‌پزشکی | روان‌شناسی | اداری | رایانه و الکترونیک | مدیریت و اداره | ایمنی و امنیت عمومی | خدمات مشتری و شخصی | پرسنل و منابع انسانی | درمان و مشاوره | ریاضیات | ارتباطات و رسانه | شیمی | قانون و دولت</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک نوشتاری | وضوح گفتار | درک شفاهی | بیان نوشتاری | استدلال قیاسی | استدلال استقرایی | دید نزدیک | تشخیص گفتار | حساسیت به مسئله | نظم‌دهی اطلاعات | روانی ایده‌ها | اصالت | توجه انتخابی | انعطاف‌پذیری دسته‌بندی</t>
+          <t>بیان شفاهی | درک کتبی | وضوح گفتار | درک شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | بینایی نزدیک | تشخیص گفتار | حساسیت به مسئله | ترتیب‌دهی اطلاعات | روانی ایده‌ها | اصالت | توجه انتخابی | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>بحث‌های رودررو با افراد و درون تیم‌ها | ایمیل | آزادی در تصمیم‌گیری | تماس با دیگران | محیط داخلی، دارای کنترل محیطی | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم | مکالمات تلفنی | سخنرانی عمومی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | تکرار تصمیم‌گیری | صرف زمان برای نشستن | اهمیت دقیق یا صحیح بودن | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | برخورد با مشتریان خارجی یا عموم مردم</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ایمیل | آزادی در تصمیم‌گیری | ارتباط با دیگران | محیط داخلی، دارای کنترل شرایط محیطی | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم | مکالمات تلفنی | سخنرانی عمومی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فراوانی تصمیم‌گیری | صرف زمان برای نشستن | اهمیت دقیق یا درست بودن | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | تعامل با مشتریان خارجی یا عموم مردم</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>پرستاران روان‌پزشکی با تمرین پیشرفته | استادان علوم زیستی، پس از متوسطه | معلمان آموزش فنی/حرفه‌ای، پس از متوسطه | متخصصان پرستاری بالینی | هماهنگ‌کنندگان پژوهش‌های بالینی | استادان آموزش و پرورش، پس از متوسطه | استادان علوم خانواده و مصرف‌کننده، پس از متوسطه | متخصصان آموزش بهداشت | متخصصان انفورماتیک سلامت | مدیران خدمات پزشکی و بهداشتی | مربیان و استادان پرستاری، پس از متوسطه | پزشکان طب پیشگیری | استادان روان‌شناسی، پس از متوسطه | استادان مطالعات تفریحی و تناسب اندام، پس از متوسطه | استادان مددکاری اجتماعی، پس از متوسطه | معلمان آموزش ویژه، مدارس ابتدایی | معلمان آموزش ویژه، مهدکودک | معلمان آموزش ویژه، مدارس متوسطه | دستیاران آموزشی، پس از متوسطه | دستیاران آموزشی، آموزش ویژه</t>
+          <t>پرستاران پیشرفته روانپزشکی | مدرسان علوم زیستی، پس از متوسطه | اساتید آموزش‌های شغلی/فنی، پس از متوسطه | متخصصان پرستاری بالینی | هماهنگ‌کنندگان تحقیقات بالینی | مدرسان علوم تربیتی، آموزش عالی | اساتید علوم خانواده و مصرف‌کننده، پس از متوسطه | متخصصان آموزش بهداشت | متخصصان انفورماتیک سلامت | مدیران خدمات پزشکی و بهداشتی | مربیان و استادان پرستاری، پس از متوسطه | پزشکان طب پیشگیری | استادان روان‌شناسی، پس از متوسطه | اساتید مطالعات تفریحی و تناسب اندام، پس از متوسطه | مدرسان مددکاری اجتماعی، آموزش عالی | معلمان آموزش ویژه، دبستان | معلمان آموزش ویژه، کودکستان | معلمان آموزش ویژه، متوسطه | دستیاران آموزشی، مقطع پس از متوسطه | دستیاران آموزشی، آموزش استثنایی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Nursing Instructors and Teachers, Postsecondary (مربیان و استادان پرستاری، پس از متوسطه)</t>
+          <t>مربیان و استادان پرستاری، پس از متوسطه (Nursing Instructors and Teachers, Postsecondary)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1016,32 +1016,32 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Blackboard Learn | نرم‌افزار Blackboard | نرم‌افزار ویرایش مشارکتی | برنامه درسی مشترک | نرم‌افزار سیستم مدیریت دوره | DOC Cop | نرم‌افزار Desire2Learn LMS | نرم‌افزار ایمیل | Google Docs | نرم‌افزار اسکن تصویر | نرم‌افزار یادگیری تعاملی | سیستم مدیریت یادگیری LMS | نرم‌افزار MEDITECH | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Moodle | نرم‌افزار گرافیک ارائه | Sakai CLE | نرم‌افزار مرورگر وب | iParadigms Turnitin</t>
+          <t>Blackboard Learn | نرم‌افزار Blackboard | نرم‌افزار ویرایش مشارکتی | Common Curriculum | نرم‌افزار سیستم مدیریت دوره | DOC Cop | نرم‌افزار Desire2Learn LMS | نرم‌افزار ایمیل | Google Docs | نرم‌افزار اسکن تصویر | نرم‌افزار یادگیری تعاملی | سیستم مدیریت یادگیری LMS | نرم‌افزار MEDITECH | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Moodle | نرم‌افزار گرافیک ارائه | Sakai CLE | نرم‌افزار مرورگر وب | iParadigms Turnitin</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>سخنرانی | راهبردهای یادگیری | نوشتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | یادگیری فعال | نظارت</t>
+          <t>سخن گفتن | راهبردهای یادگیری | نگارش | گوش دادن فعال | درک مطلب | تفکر انتقادی | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | آموزش و پرورش | روان‌شناسی | زبان انگلیسی | زیست‌شناسی | خدمات مشتری و شخصی | ریاضیات | درمان و مشاوره | جامعه‌شناسی و انسان‌شناسی | رایانه و الکترونیک | اداری | ارتباطات و رسانه | ایمنی و امنیت عمومی | مدیریت و اداره</t>
+          <t>پزشکی و دندان‌پزشکی | آموزش و پرورش | روان‌شناسی | زبان انگلیسی | زیست‌شناسی | خدمات مشتری و شخصی | ریاضیات | درمان و مشاوره | جامعه‌شناسی و انسان‌شناسی | رایانه و الکترونیک | اداری | ارتباطات و رسانه | ایمنی و امنیت عمومی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک نوشتاری | بیان شفاهی | بیان نوشتاری | وضوح گفتار | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | دید نزدیک | تشخیص گفتار | نظم‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | توجه انتخابی | انعطاف‌پذیری بستار | استدلال ریاضی | اصالت</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | وضوح گفتار | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | بینایی نزدیک | تشخیص گفتار | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | توجه انتخابی | انعطاف‌پذیری بستار | استدلال ریاضی | اصالت</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>ایمیل | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا صحیح بودن | تماس با دیگران | بحث‌های رودررو با افراد و درون تیم‌ها | برخورد با مشتریان خارجی یا عموم مردم | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | مکالمات تلفنی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | محیط داخلی، دارای کنترل محیطی | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | تکرار تصمیم‌گیری | نتایج کاری و خروجی‌های سایر کارکنان | سخنرانی عمومی | سلامت و ایمنی سایر کارکنان | فشار زمانی | نزدیکی فیزیکی | پیامد خطا | نامه‌ها و یادداشت‌های کتبی</t>
+          <t>ایمیل | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا درست بودن | ارتباط با دیگران | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تعامل با مشتریان خارجی یا عموم مردم | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | مکالمات تلفنی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | محیط داخلی، دارای کنترل شرایط محیطی | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | فراوانی تصمیم‌گیری | پیامدهای کاری و نتایج سایر کارکنان | سخنرانی عمومی | سلامت و ایمنی سایر کارکنان | فشار زمانی | نزدیکی فیزیکی | پیامد خطا | نامه‌ها و یادداشت‌های کتبی</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>پرستاران مراقبت‌های حاد | پرستاران روان‌پزشکی با تمرین پیشرفته | متخصصان پرستاری بالینی | پرستاران مراقبت‌های ویژه | استادان آموزش و پرورش، پس از متوسطه | متخصصان آموزش بهداشت | متخصصان انفورماتیک سلامت | استادان تخصص‌های بهداشتی، پس از متوسطه | پرستاران عملی دارای مجوز و پرستاران حرفه‌ای دارای مجوز | مدیران خدمات پزشکی و بهداشتی | ماماها | پرستاران متخصص | استادان روان‌شناسی، پس از متوسطه | پرستاران ثبت‌نام شده | معلمان آموزش ویژه، مدارس ابتدایی | معلمان آموزش ویژه، مهدکودک | دستیاران آموزشی، پس از متوسطه | دستیاران آموزشی، پیش‌دبستانی، ابتدایی، راهنمایی و متوسطه، به جز آموزش ویژه | دستیاران آموزشی، آموزش ویژه | معلمان خصوصی</t>
+          <t>پرستاران مراقبت‌های ویژه | پرستاران پیشرفته روانپزشکی | متخصصان پرستاری بالینی | پرستاران بخش مراقبت‌های ویژه | مدرسان علوم تربیتی، آموزش عالی | متخصصان آموزش بهداشت | متخصصان انفورماتیک سلامت | استادان تخصص‌های بهداشتی، پس از متوسطه | پرستاران عملی دارای مجوز و پرستاران حرفه‌ای دارای مجوز | مدیران خدمات پزشکی و بهداشتی | ماماها | پرستاران متخصص | استادان روان‌شناسی، پس از متوسطه | پرستاران ثبت‌شده | معلمان آموزش ویژه، دبستان | معلمان آموزش ویژه، کودکستان | دستیاران آموزشی، مقطع پس از متوسطه | دستیاران آموزشی، پیش‌دبستانی، ابتدایی، راهنمایی و متوسطه، به جز آموزش استثنایی | دستیاران آموزشی، آموزش استثنایی | معلمان خصوصی</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0032_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0032_fa.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>سخن گفتن | درک مطلب | نگارش | شنیدن فعال | راهبردهای یادگیری | یادگیری فعال | تفکر انتقادی | نظارت | علوم پایه</t>
+          <t>سخن گفتن | درک مطلب | نگارش | گوش دادن فعال | راهبردهای یادگیری | یادگیری فعال | تفکر انتقادی | نظارت | علوم</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>جامعه‌شناسی و انسان‌شناسی | تاریخ و باستان‌شناسی | زبان انگلیسی | آموزش و تدریس | جغرافیا | فلسفه و الهیات | زبان‌های خارجی | ارتباطات و رسانه | امور اداری و دفتری</t>
+          <t>جامعه‌شناسی و انسان‌شناسی | تاریخ و باستان‌شناسی | زبان انگلیسی | آموزش و پرورش | جغرافیا | فلسفه و الهیات | زبان خارجی | ارتباطات و رسانه | اداری</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>بیان شفاهی | وضوح گفتار | بیان کتبی | درک کتبی | درک شفاهی | دید نزدیک | استدلال استقرایی | استدلال قیاسی | مرتب‌سازی اطلاعات | تشخیص گفتار | روانی کلام و سیالی ایده‌ها | انعطاف‌پذیری در طبقه‌بندی | حساسیت به مسئله | ابتکار و اصالت | توجه انتخابی | حافظه و به‌خاطرسپاری | دید دور | تقسیم توجه | تشخیص الگوها</t>
+          <t>بیان شفاهی | وضوح گفتار | بیان کتبی | درک کتبی | درک شفاهی | بینایی نزدیک | استدلال استقرایی | استدلال قیاسی | ترتیب‌دهی اطلاعات | تشخیص گفتار | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | حساسیت به مسئله | اصالت | توجه انتخابی | حفظ کردن | بینایی دور | تقسیم توجه | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>انسان‌شناسان و باستان‌شناسان | استادان مطالعات منطقه‌ای، قومی و فرهنگی دانشگاه | استادان علوم جوی، زمین‌شناسی، علوم دریایی و فضا در دانشگاه | استادان علوم زیستی دانشگاه | استادان علوم ارتباطات دانشگاه | استادان علوم تربیتی دانشگاه | آموزگاران دوره ابتدایی (به‌جز آموزش استثنایی) | استادان زبان و ادبیات انگلیسی دانشگاه | استادان علوم محیط‌زیست دانشگاه | استادان علوم خانواده و مصرف‌کننده در دانشگاه | استادان جغرافیای دانشگاه | استادان تاریخ دانشگاه | معلمان دوره اول متوسطه (به‌جز آموزش استثنایی و فنی‌وحرفه‌ای) | استادان فلسفه و دین دانشگاه | استادان علوم سیاسی دانشگاه | استادان روان‌شناسی دانشگاه | معلمان دوره دوم متوسطه (به‌جز آموزش استثنایی و فنی‌وحرفه‌ای) | استادان مددکاری اجتماعی دانشگاه | استادان جامعه‌شناسی دانشگاه | دستیاران آموزشی دانشگاه</t>
+          <t>انسان‌شناسان و باستان‌شناسان | استادان مطالعات منطقه‌ای، قومی و فرهنگی دانشگاه | استادان و مدرسان علوم جوی، زمین، دریا و فضا در دانشگاه‌ها و مراکز آموزش عالی | استادان و مدرسان علوم زیستی در دانشگاه‌ها و مراکز آموزش عالی | مدرسان علوم ارتباطات در دانشگاه‌ها و مراکز آموزش عالی | مدرسان علوم تربیتی و آموزش در دانشگاه‌ها و مراکز آموزش عالی | معلمان دوره ابتدایی، به‌جز آموزش استثنایی | مدرسان زبان و ادبیات انگلیسی در دانشگاه‌ها و مراکز آموزش عالی | استادان و مدرسان علوم محیط‌زیست در دانشگاه‌ها و مراکز آموزش عالی | مدرسان علوم خانواده و مدیریت مصرف در آموزش عالی | استادان جغرافیای دانشگاه | مدرسان تاریخ در دانشگاه‌ها و مراکز آموزش عالی | معلمان دوره اول متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | مدرسان فلسفه و الهیات در آموزش عالی | استادان علوم سیاسی دانشگاه | استادان روان‌شناسی دانشگاه | دبیران دوره دوم متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | مدرسان مددکاری اجتماعی در دانشگاه‌ها و مراکز آموزش عالی | استادان جامعه‌شناسی دانشگاه | دستیاران آموزشی در آموزش عالی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>درک مطلب | سخن گفتن | راهبردهای یادگیری | یادگیری فعال | نگارش | شنیدن فعال | تفکر انتقادی | نظارت</t>
+          <t>درک مطلب | سخن گفتن | راهبردهای یادگیری | یادگیری فعال | نگارش | گوش دادن فعال | تفکر انتقادی | نظارت</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>آموزش و تدریس | زبان انگلیسی | جامعه‌شناسی و انسان‌شناسی | تاریخ و باستان‌شناسی | زبان‌های خارجی | ارتباطات و رسانه | رایانه و الکترونیک | فلسفه و الهیات | امور اداری و دفتری</t>
+          <t>آموزش و پرورش | زبان انگلیسی | جامعه‌شناسی و انسان‌شناسی | تاریخ و باستان‌شناسی | زبان خارجی | ارتباطات و رسانه | رایانه و الکترونیک | فلسفه و الهیات | اداری</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>بیان شفاهی | بیان کتبی | وضوح گفتار | درک شفاهی | درک کتبی | استدلال استقرایی | دید نزدیک | استدلال قیاسی | تشخیص گفتار | حساسیت به مسئله | ابتکار و اصالت | روانی کلام و سیالی ایده‌ها | انعطاف‌پذیری در طبقه‌بندی | مرتب‌سازی اطلاعات</t>
+          <t>بیان شفاهی | بیان کتبی | وضوح گفتار | درک شفاهی | درک کتبی | استدلال استقرایی | بینایی نزدیک | استدلال قیاسی | تشخیص گفتار | حساسیت به مسئله | اصالت | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>مدرسان آموزش پایه بزرگسالان، متوسطه بزرگسالان و آموزش زبان انگلیسی | استادان انسان‌شناسی و باستان‌شناسی دانشگاه | استادان علوم ارتباطات دانشگاه | استادان علوم تربیتی دانشگاه | آموزگاران دوره ابتدایی (به‌جز آموزش استثنایی) | استادان زبان و ادبیات انگلیسی دانشگاه | استادان علوم خانواده و مصرف‌کننده در دانشگاه | استادان زبان و ادبیات خارجی دانشگاه | استادان جغرافیای دانشگاه | استادان تاریخ دانشگاه | استادان حقوق دانشگاه | استادان علم اطلاعات و دانش‌شناسی دانشگاه | معلمان دوره اول متوسطه (به‌جز آموزش استثنایی و فنی‌وحرفه‌ای) | استادان فلسفه و دین دانشگاه | استادان علوم سیاسی دانشگاه | استادان روان‌شناسی دانشگاه | معلمان دوره دوم متوسطه (به‌جز آموزش استثنایی و فنی‌وحرفه‌ای) | استادان مددکاری اجتماعی دانشگاه | استادان جامعه‌شناسی دانشگاه | دستیاران آموزشی دانشگاه</t>
+          <t>مربیان سوادآموزی بزرگسالان، دوره اول و دوم متوسطه بزرگسالان و زبان دوم | استادان انسان‌شناسی و باستان‌شناسی دانشگاه | مدرسان علوم ارتباطات در دانشگاه‌ها و مراکز آموزش عالی | مدرسان علوم تربیتی و آموزش در دانشگاه‌ها و مراکز آموزش عالی | معلمان دوره ابتدایی، به‌جز آموزش استثنایی | مدرسان زبان و ادبیات انگلیسی در دانشگاه‌ها و مراکز آموزش عالی | مدرسان علوم خانواده و مدیریت مصرف در آموزش عالی | مدرسان زبان و ادبیات خارجی در دانشگاه‌ها و مراکز آموزش عالی | استادان جغرافیای دانشگاه | مدرسان تاریخ در دانشگاه‌ها و مراکز آموزش عالی | مدرسان حقوق در دانشگاه‌ها و مراکز آموزش عالی | مدرسان علم اطلاعات و دانش‌شناسی در دانشگاه‌ها و مراکز آموزش عالی | معلمان دوره اول متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | مدرسان فلسفه و الهیات در آموزش عالی | استادان علوم سیاسی دانشگاه | استادان روان‌شناسی دانشگاه | دبیران دوره دوم متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | مدرسان مددکاری اجتماعی در دانشگاه‌ها و مراکز آموزش عالی | استادان جامعه‌شناسی دانشگاه | دستیاران آموزشی در آموزش عالی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | درک مطلب | نگارش | تفکر انتقادی | راهبردهای یادگیری | یادگیری فعال | ریاضیات | نظارت</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | نگارش | تفکر انتقادی | راهبردهای یادگیری | یادگیری فعال | ریاضیات | نظارت</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ریاضیات | آموزش و تدریس | اقتصاد و حسابداری | زبان انگلیسی</t>
+          <t>ریاضیات | آموزش و پرورش | اقتصاد و حسابداری | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>بیان شفاهی | وضوح گفتار | درک شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | دید نزدیک | حساسیت به مسئله | استدلال ریاضی | محاسبات عددی | مرتب‌سازی اطلاعات | روانی کلام و سیالی ایده‌ها | انعطاف‌پذیری در طبقه‌بندی | ابتکار و اصالت | حافظه و به‌خاطرسپاری</t>
+          <t>بیان شفاهی | وضوح گفتار | درک شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | بینایی نزدیک | حساسیت به مسئله | استدلال ریاضی | توانایی عددی | ترتیب‌دهی اطلاعات | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | اصالت | حفظ کردن</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>استادان علوم کشاورزی دانشگاه | استادان انسان‌شناسی و باستان‌شناسی دانشگاه | استادان مطالعات منطقه‌ای، قومی و فرهنگی دانشگاه | استادان مدیریت و بازرگانی دانشگاه | معلمان دروس حرفه‌ای و مهارتی دوره اول متوسطه | اقتصاددانان | مدیران امور آموزشی دانشگاه | استادان علوم تربیتی دانشگاه | اقتصاددانان محیط‌زیست | استادان علوم محیط‌زیست دانشگاه | استادان علوم خانواده و مصرف‌کننده در دانشگاه | استادان جنگل‌داری و حفاظت منابع طبیعی دانشگاه | استادان جغرافیای دانشگاه | استادان حقوق دانشگاه | استادان علوم ریاضی دانشگاه | استادان علوم سیاسی دانشگاه | استادان روان‌شناسی دانشگاه | استادان مددکاری اجتماعی دانشگاه | استادان جامعه‌شناسی دانشگاه | دستیاران آموزشی دانشگاه</t>
+          <t>استادان و مدرسان علوم کشاورزی در دانشگاه‌ها و مراکز آموزش عالی | استادان انسان‌شناسی و باستان‌شناسی دانشگاه | استادان مطالعات منطقه‌ای، قومی و فرهنگی دانشگاه | استادان علوم اداری و مدیریت، آموزش عالی | معلمان آموزش‌های فنی و حرفه‌ای در دوره اول متوسطه | اقتصاددانان | مدیران آموزش عالی | مدرسان علوم تربیتی و آموزش در دانشگاه‌ها و مراکز آموزش عالی | اقتصاددانان محیط زیست | استادان و مدرسان علوم محیط‌زیست در دانشگاه‌ها و مراکز آموزش عالی | مدرسان علوم خانواده و مدیریت مصرف در آموزش عالی | استادان و مدرسان جنگلداری و منابع طبیعی در دانشگاه‌ها و مراکز آموزش عالی | استادان جغرافیای دانشگاه | مدرسان حقوق در دانشگاه‌ها و مراکز آموزش عالی | استادان و مدرسان علوم ریاضی در دانشگاه‌ها و مراکز آموزش عالی | استادان علوم سیاسی دانشگاه | استادان روان‌شناسی دانشگاه | مدرسان مددکاری اجتماعی در دانشگاه‌ها و مراکز آموزش عالی | استادان جامعه‌شناسی دانشگاه | دستیاران آموزشی در آموزش عالی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>نگارش | سخن گفتن | شنیدن فعال | درک مطلب | تفکر انتقادی | یادگیری فعال | راهبردهای یادگیری | علوم پایه | نظارت</t>
+          <t>نگارش | سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | یادگیری فعال | راهبردهای یادگیری | علوم | نظارت</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | جغرافیا | آموزش و تدریس | تاریخ و باستان‌شناسی | ریاضیات | رایانه و الکترونیک | جامعه‌شناسی و انسان‌شناسی</t>
+          <t>زبان انگلیسی | جغرافیا | آموزش و پرورش | تاریخ و باستان‌شناسی | ریاضیات | رایانه و الکترونیک | جامعه‌شناسی و انسان‌شناسی</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>بیان شفاهی | بیان کتبی | درک شفاهی | درک کتبی | وضوح گفتار | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | حساسیت به مسئله | دید نزدیک | مرتب‌سازی اطلاعات | روانی کلام و سیالی ایده‌ها | انعطاف‌پذیری در طبقه‌بندی | ابتکار و اصالت</t>
+          <t>بیان شفاهی | بیان کتبی | درک شفاهی | درک کتبی | وضوح گفتار | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | حساسیت به مسئله | بینایی نزدیک | ترتیب‌دهی اطلاعات | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | اصالت</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>مدرسان آموزش پایه بزرگسالان، متوسطه بزرگسالان و آموزش زبان انگلیسی | استادان انسان‌شناسی و باستان‌شناسی دانشگاه | استادان مطالعات منطقه‌ای، قومی و فرهنگی دانشگاه | استادان علوم جوی، زمین‌شناسی، علوم دریایی و فضا در دانشگاه | استادان علوم زیستی دانشگاه | استادان اقتصاد دانشگاه | استادان علوم تربیتی دانشگاه | آموزگاران دوره ابتدایی (به‌جز آموزش استثنایی) | استادان علوم محیط‌زیست دانشگاه | استادان جنگل‌داری و حفاظت منابع طبیعی دانشگاه | جغرافیادانان | استادان تاریخ دانشگاه | استادان علم اطلاعات و دانش‌شناسی دانشگاه | استادان علوم ریاضی دانشگاه | معلمان دوره اول متوسطه (به‌جز آموزش استثنایی و فنی‌وحرفه‌ای) | استادان علوم سیاسی دانشگاه | معلمان دوره دوم متوسطه (به‌جز آموزش استثنایی و فنی‌وحرفه‌ای) | استادان جامعه‌شناسی دانشگاه | معلمان آموزش استثنایی دوره ابتدایی | دستیاران آموزشی دانشگاه</t>
+          <t>مربیان سوادآموزی بزرگسالان، دوره اول و دوم متوسطه بزرگسالان و زبان دوم | استادان انسان‌شناسی و باستان‌شناسی دانشگاه | استادان مطالعات منطقه‌ای، قومی و فرهنگی دانشگاه | استادان و مدرسان علوم جوی، زمین، دریا و فضا در دانشگاه‌ها و مراکز آموزش عالی | استادان و مدرسان علوم زیستی در دانشگاه‌ها و مراکز آموزش عالی | استادان اقتصاد دانشگاه | مدرسان علوم تربیتی و آموزش در دانشگاه‌ها و مراکز آموزش عالی | معلمان دوره ابتدایی، به‌جز آموزش استثنایی | استادان و مدرسان علوم محیط‌زیست در دانشگاه‌ها و مراکز آموزش عالی | استادان و مدرسان جنگلداری و منابع طبیعی در دانشگاه‌ها و مراکز آموزش عالی | جغرافیدانان | مدرسان تاریخ در دانشگاه‌ها و مراکز آموزش عالی | مدرسان علم اطلاعات و دانش‌شناسی در دانشگاه‌ها و مراکز آموزش عالی | استادان و مدرسان علوم ریاضی در دانشگاه‌ها و مراکز آموزش عالی | معلمان دوره اول متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | استادان علوم سیاسی دانشگاه | دبیران دوره دوم متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | استادان جامعه‌شناسی دانشگاه | معلمان آموزش استثنایی دوره ابتدایی | دستیاران آموزشی در آموزش عالی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>سخن گفتن | درک مطلب | یادگیری فعال | نگارش | شنیدن فعال | تفکر انتقادی | راهبردهای یادگیری | نظارت</t>
+          <t>سخن گفتن | درک مطلب | یادگیری فعال | نگارش | گوش دادن فعال | تفکر انتقادی | راهبردهای یادگیری | نظارت</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | حقوق و امور دولتی | آموزش و تدریس | تاریخ و باستان‌شناسی | جامعه‌شناسی و انسان‌شناسی | جغرافیا | فلسفه و الهیات</t>
+          <t>زبان انگلیسی | قانون و دولت | آموزش و پرورش | تاریخ و باستان‌شناسی | جامعه‌شناسی و انسان‌شناسی | جغرافیا | فلسفه و الهیات</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک کتبی | درک شفاهی | بیان شفاهی | بیان کتبی | وضوح گفتار | استدلال استقرایی | دید نزدیک | تشخیص گفتار | استدلال قیاسی | حساسیت به مسئله | توجه انتخابی | انعطاف‌پذیری در طبقه‌بندی | مرتب‌سازی اطلاعات | ابتکار و اصالت | روانی کلام و سیالی ایده‌ها</t>
+          <t>درک کتبی | درک شفاهی | بیان شفاهی | بیان کتبی | وضوح گفتار | استدلال استقرایی | بینایی نزدیک | تشخیص گفتار | استدلال قیاسی | حساسیت به مسئله | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | اصالت | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>استادان انسان‌شناسی و باستان‌شناسی دانشگاه | استادان مطالعات منطقه‌ای، قومی و فرهنگی دانشگاه | استادان مدیریت و بازرگانی دانشگاه | استادان علوم ارتباطات دانشگاه | استادان علوم انتظامی و حقوق کیفری دانشگاه | استادان اقتصاد دانشگاه | استادان علوم تربیتی دانشگاه | استادان زبان و ادبیات انگلیسی دانشگاه | استادان علوم خانواده و مصرف‌کننده در دانشگاه | استادان جغرافیای دانشگاه | استادان تاریخ دانشگاه | استادان حقوق دانشگاه | استادان علم اطلاعات و دانش‌شناسی دانشگاه | استادان فلسفه و دین دانشگاه | کارشناسان و تحلیل‌گران علوم سیاسی | استادان روان‌شناسی دانشگاه | استادان مددکاری اجتماعی دانشگاه | جامعه‌شناسان | استادان جامعه‌شناسی دانشگاه | معلمان آموزش استثنایی دوره ابتدایی</t>
+          <t>استادان انسان‌شناسی و باستان‌شناسی دانشگاه | استادان مطالعات منطقه‌ای، قومی و فرهنگی دانشگاه | استادان علوم اداری و مدیریت، آموزش عالی | مدرسان علوم ارتباطات در دانشگاه‌ها و مراکز آموزش عالی | مدرسان حقوق جزا، جرم‌شناسی و علوم انتظامی در دانشگاه‌ها و مراکز آموزش عالی | استادان اقتصاد دانشگاه | مدرسان علوم تربیتی و آموزش در دانشگاه‌ها و مراکز آموزش عالی | مدرسان زبان و ادبیات انگلیسی در دانشگاه‌ها و مراکز آموزش عالی | مدرسان علوم خانواده و مدیریت مصرف در آموزش عالی | استادان جغرافیای دانشگاه | مدرسان تاریخ در دانشگاه‌ها و مراکز آموزش عالی | مدرسان حقوق در دانشگاه‌ها و مراکز آموزش عالی | مدرسان علم اطلاعات و دانش‌شناسی در دانشگاه‌ها و مراکز آموزش عالی | مدرسان فلسفه و الهیات در آموزش عالی | دانشمندان و پژوهشگران علوم سیاسی | استادان روان‌شناسی دانشگاه | مدرسان مددکاری اجتماعی در دانشگاه‌ها و مراکز آموزش عالی | جامعه‌شناسان | استادان جامعه‌شناسی دانشگاه | معلمان آموزش استثنایی دوره ابتدایی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>راهبردهای یادگیری | درک مطلب | سخن گفتن | نگارش | شنیدن فعال | تفکر انتقادی | یادگیری فعال | نظارت | علوم پایه | ریاضیات</t>
+          <t>راهبردهای یادگیری | درک مطلب | سخن گفتن | نگارش | گوش دادن فعال | تفکر انتقادی | یادگیری فعال | نظارت | علوم | ریاضیات</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>روان‌شناسی | زبان انگلیسی | آموزش و تدریس | جامعه‌شناسی و انسان‌شناسی | ریاضیات | درمان و مشاوره | رایانه و الکترونیک | ارتباطات و رسانه | زیست‌شناسی</t>
+          <t>روان‌شناسی | زبان انگلیسی | آموزش و پرورش | جامعه‌شناسی و انسان‌شناسی | ریاضیات | درمان و مشاوره | رایانه و الکترونیک | ارتباطات و رسانه | زیست‌شناسی</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>بیان شفاهی | بیان کتبی | درک کتبی | وضوح گفتار | درک شفاهی | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | حساسیت به مسئله | دید نزدیک | روانی کلام و سیالی ایده‌ها | انعطاف‌پذیری در طبقه‌بندی | مرتب‌سازی اطلاعات | ابتکار و اصالت</t>
+          <t>بیان شفاهی | بیان کتبی | درک کتبی | وضوح گفتار | درک شفاهی | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | حساسیت به مسئله | بینایی نزدیک | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | اصالت</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>استادان انسان‌شناسی و باستان‌شناسی دانشگاه | استادان علوم زیستی دانشگاه | استادان اقتصاد دانشگاه | استادان علوم تربیتی دانشگاه | آموزگاران دوره ابتدایی (به‌جز آموزش استثنایی) | استادان علوم خانواده و مصرف‌کننده در دانشگاه | استادان تخصص‌های علوم پزشکی و بهداشت دانشگاه | استادان علوم ریاضی دانشگاه | معلمان دوره اول متوسطه (به‌جز آموزش استثنایی و فنی‌وحرفه‌ای) | مربیان و استادان پرستاری دانشگاه | استادان فلسفه و دین دانشگاه | استادان علوم ورزشی و تربیت بدنی دانشگاه | روان‌شناسان مدرسه | معلمان دوره دوم متوسطه (به‌جز آموزش استثنایی و فنی‌وحرفه‌ای) | استادان مددکاری اجتماعی دانشگاه | استادان جامعه‌شناسی دانشگاه | معلمان آموزش استثنایی دوره ابتدایی | معلمان آموزش استثنایی دوره پیش‌دبستانی | دستیاران آموزشی دانشگاه | معلمان خصوصی و مدرسان تقویتی</t>
+          <t>استادان انسان‌شناسی و باستان‌شناسی دانشگاه | استادان و مدرسان علوم زیستی در دانشگاه‌ها و مراکز آموزش عالی | استادان اقتصاد دانشگاه | مدرسان علوم تربیتی و آموزش در دانشگاه‌ها و مراکز آموزش عالی | معلمان دوره ابتدایی، به‌جز آموزش استثنایی | مدرسان علوم خانواده و مدیریت مصرف در آموزش عالی | استادان تخصص‌های علوم پزشکی و بهداشت دانشگاه | استادان و مدرسان علوم ریاضی در دانشگاه‌ها و مراکز آموزش عالی | معلمان دوره اول متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | مربیان و استادان پرستاری دانشگاه | مدرسان فلسفه و الهیات در آموزش عالی | مدرسان علوم ورزشی، تربیت بدنی و اوقات فراغت در آموزش عالی | روان‌شناسان مدارس | دبیران دوره دوم متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | مدرسان مددکاری اجتماعی در دانشگاه‌ها و مراکز آموزش عالی | استادان جامعه‌شناسی دانشگاه | معلمان آموزش استثنایی دوره ابتدایی | معلمان آموزش استثنایی دوره آمادگی و نوآموزان | دستیاران آموزشی در آموزش عالی | معلمان خصوصی و مدرسان تقویتی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>سخن گفتن | راهبردهای یادگیری | نگارش | شنیدن فعال | درک مطلب | تفکر انتقادی | نظارت | یادگیری فعال</t>
+          <t>سخن گفتن | راهبردهای یادگیری | نگارش | گوش دادن فعال | درک مطلب | تفکر انتقادی | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | جامعه‌شناسی و انسان‌شناسی | آموزش و تدریس | رایانه و الکترونیک | تاریخ و باستان‌شناسی | روان‌شناسی | فلسفه و الهیات | حقوق و امور دولتی | ریاضیات | ارتباطات و رسانه | خدمات مشتریان و خدمات فردی | امور اداری و دفتری | جغرافیا</t>
+          <t>زبان انگلیسی | جامعه‌شناسی و انسان‌شناسی | آموزش و پرورش | رایانه و الکترونیک | تاریخ و باستان‌شناسی | روان‌شناسی | فلسفه و الهیات | قانون و دولت | ریاضیات | ارتباطات و رسانه | خدمات مشتری و شخصی | اداری | جغرافیا</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | استدلال استقرایی | وضوح گفتار | استدلال قیاسی | دید نزدیک | تشخیص گفتار | مرتب‌سازی اطلاعات | انعطاف‌پذیری در طبقه‌بندی | روانی کلام و سیالی ایده‌ها | حساسیت به مسئله | ابتکار و اصالت</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | استدلال استقرایی | وضوح گفتار | استدلال قیاسی | بینایی نزدیک | تشخیص گفتار | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | حساسیت به مسئله | اصالت</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>استادان انسان‌شناسی و باستان‌شناسی دانشگاه | استادان مطالعات منطقه‌ای، قومی و فرهنگی دانشگاه | استادان علوم ارتباطات دانشگاه | استادان علوم انتظامی و حقوق کیفری دانشگاه | استادان اقتصاد دانشگاه | استادان علوم تربیتی دانشگاه | استادان زبان و ادبیات انگلیسی دانشگاه | استادان علوم خانواده و مصرف‌کننده در دانشگاه | استادان جغرافیای دانشگاه | استادان تاریخ دانشگاه | استادان حقوق دانشگاه | استادان علم اطلاعات و دانش‌شناسی دانشگاه | معلمان دوره اول متوسطه (به‌جز آموزش استثنایی و فنی‌وحرفه‌ای) | استادان فلسفه و دین دانشگاه | استادان علوم سیاسی دانشگاه | استادان روان‌شناسی دانشگاه | معلمان دوره دوم متوسطه (به‌جز آموزش استثنایی و فنی‌وحرفه‌ای) | استادان مددکاری اجتماعی دانشگاه | جامعه‌شناسان | دستیاران آموزشی دانشگاه</t>
+          <t>استادان انسان‌شناسی و باستان‌شناسی دانشگاه | استادان مطالعات منطقه‌ای، قومی و فرهنگی دانشگاه | مدرسان علوم ارتباطات در دانشگاه‌ها و مراکز آموزش عالی | مدرسان حقوق جزا، جرم‌شناسی و علوم انتظامی در دانشگاه‌ها و مراکز آموزش عالی | استادان اقتصاد دانشگاه | مدرسان علوم تربیتی و آموزش در دانشگاه‌ها و مراکز آموزش عالی | مدرسان زبان و ادبیات انگلیسی در دانشگاه‌ها و مراکز آموزش عالی | مدرسان علوم خانواده و مدیریت مصرف در آموزش عالی | استادان جغرافیای دانشگاه | مدرسان تاریخ در دانشگاه‌ها و مراکز آموزش عالی | مدرسان حقوق در دانشگاه‌ها و مراکز آموزش عالی | مدرسان علم اطلاعات و دانش‌شناسی در دانشگاه‌ها و مراکز آموزش عالی | معلمان دوره اول متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | مدرسان فلسفه و الهیات در آموزش عالی | استادان علوم سیاسی دانشگاه | استادان روان‌شناسی دانشگاه | دبیران دوره دوم متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | مدرسان مددکاری اجتماعی در دانشگاه‌ها و مراکز آموزش عالی | جامعه‌شناسان | دستیاران آموزشی در آموزش عالی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | درک مطلب | تفکر انتقادی | راهبردهای یادگیری | نگارش | یادگیری فعال | نظارت</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | راهبردهای یادگیری | نگارش | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>جامعه‌شناسی و انسان‌شناسی | زبان انگلیسی | آموزش و تدریس | تاریخ و باستان‌شناسی | روان‌شناسی | حقوق و امور دولتی | فلسفه و الهیات | ارتباطات و رسانه | رایانه و الکترونیک</t>
+          <t>جامعه‌شناسی و انسان‌شناسی | زبان انگلیسی | آموزش و پرورش | تاریخ و باستان‌شناسی | روان‌شناسی | قانون و دولت | فلسفه و الهیات | ارتباطات و رسانه | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | حساسیت به مسئله | دید نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری در طبقه‌بندی | روانی کلام و سیالی ایده‌ها | ابتکار و اصالت | توجه انتخابی | تقسیم توجه | تجسم فضایی | حافظه و به‌خاطرسپاری</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | توجه انتخابی | تقسیم توجه | تجسم | حفظ کردن</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>استادان جامعه‌شناسی دانشگاه | استادان علوم سیاسی دانشگاه | استادان روان‌شناسی دانشگاه | استادان اقتصاد دانشگاه | استادان جغرافیای دانشگاه | استادان انسان‌شناسی و باستان‌شناسی دانشگاه | استادان مطالعات منطقه‌ای، قومی و فرهنگی دانشگاه | استادان تاریخ دانشگاه | استادان فلسفه و دین دانشگاه | استادان مددکاری اجتماعی دانشگاه | استادان علوم انتظامی و حقوق کیفری دانشگاه | استادان علوم تربیتی دانشگاه | استادان علوم ارتباطات دانشگاه | استادان مدیریت و بازرگانی دانشگاه | استادان حقوق دانشگاه | سایر مدرسان و استادان دانشگاه | جامعه‌شناسان | کارشناسان و تحلیل‌گران علوم سیاسی | مدیران امور آموزشی دانشگاه | هماهنگ‌کنندگان و کارشناسان برنامه‌ریزی درسی</t>
+          <t>استادان جامعه‌شناسی دانشگاه | استادان علوم سیاسی دانشگاه | استادان روان‌شناسی دانشگاه | استادان اقتصاد دانشگاه | استادان جغرافیای دانشگاه | استادان انسان‌شناسی و باستان‌شناسی دانشگاه | استادان مطالعات منطقه‌ای، قومی و فرهنگی دانشگاه | مدرسان تاریخ در دانشگاه‌ها و مراکز آموزش عالی | مدرسان فلسفه و الهیات در آموزش عالی | مدرسان مددکاری اجتماعی در دانشگاه‌ها و مراکز آموزش عالی | مدرسان حقوق جزا، جرم‌شناسی و علوم انتظامی در دانشگاه‌ها و مراکز آموزش عالی | مدرسان علوم تربیتی و آموزش در دانشگاه‌ها و مراکز آموزش عالی | مدرسان علوم ارتباطات در دانشگاه‌ها و مراکز آموزش عالی | استادان علوم اداری و مدیریت، آموزش عالی | مدرسان حقوق در دانشگاه‌ها و مراکز آموزش عالی | سایر مدرسان در آموزش عالی | جامعه‌شناسان | دانشمندان و پژوهشگران علوم سیاسی | مدیران آموزش عالی | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>درک مطلب | سخن گفتن | نگارش | شنیدن فعال | راهبردهای یادگیری | یادگیری فعال | تفکر انتقادی | نظارت | علوم پایه | ریاضیات</t>
+          <t>درک مطلب | سخن گفتن | نگارش | گوش دادن فعال | راهبردهای یادگیری | یادگیری فعال | تفکر انتقادی | نظارت | علوم | ریاضیات</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>آموزش و تدریس | زبان انگلیسی | زیست‌شناسی | پزشکی و دندان‌پزشکی | روان‌شناسی | امور اداری و دفتری | رایانه و الکترونیک | مدیریت و امور اداری | ایمنی و امنیت عمومی | خدمات مشتریان و خدمات فردی | امور اداری و منابع انسانی | درمان و مشاوره | ریاضیات | ارتباطات و رسانه | شیمی | حقوق و امور دولتی</t>
+          <t>آموزش و پرورش | زبان انگلیسی | زیست‌شناسی | پزشکی و دندان‌پزشکی | روان‌شناسی | اداری | رایانه و الکترونیک | مدیریت و اداره | ایمنی و امنیت عمومی | خدمات مشتری و شخصی | پرسنل و منابع انسانی | درمان و مشاوره | ریاضیات | ارتباطات و رسانه | شیمی | قانون و دولت</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک کتبی | وضوح گفتار | درک شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | دید نزدیک | تشخیص گفتار | حساسیت به مسئله | مرتب‌سازی اطلاعات | روانی کلام و سیالی ایده‌ها | ابتکار و اصالت | توجه انتخابی | انعطاف‌پذیری در طبقه‌بندی</t>
+          <t>بیان شفاهی | درک کتبی | وضوح گفتار | درک شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | بینایی نزدیک | تشخیص گفتار | حساسیت به مسئله | ترتیب‌دهی اطلاعات | روانی ایده‌ها | اصالت | توجه انتخابی | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>پرستاران پیشرفته روان‌پزشکی | استادان علوم زیستی دانشگاه | مربیان آموزش‌های فنی و حرفه‌ای دانشگاهی | متخصصان بالینی پرستاری | کارشناسان هماهنگ‌کننده پژوهش‌های بالینی | استادان علوم تربیتی دانشگاه | استادان علوم خانواده و مصرف‌کننده در دانشگاه | کارشناسان آموزش سلامت و بهداشت | متخصصان انفورماتیک سلامت | مدیران خدمات درمانی و بهداشتی | مربیان و استادان پرستاری دانشگاه | پزشکان طب پیشگیری و پزشکی اجتماعی | استادان روان‌شناسی دانشگاه | استادان علوم ورزشی و تربیت بدنی دانشگاه | استادان مددکاری اجتماعی دانشگاه | معلمان آموزش استثنایی دوره ابتدایی | معلمان آموزش استثنایی دوره پیش‌دبستانی | معلمان آموزش استثنایی دوره متوسطه | دستیاران آموزشی دانشگاه | دستیاران آموزشی آموزش استثنایی</t>
+          <t>پرستاران تخصصی روانپزشکی | استادان و مدرسان علوم زیستی در دانشگاه‌ها و مراکز آموزش عالی | مدرسان آموزش‌های فنی و حرفه‌ای در آموزش عالی | پرستاران متخصص بالینی | هماهنگ‌کنندگان کارآزمایی‌های بالینی | مدرسان علوم تربیتی و آموزش در دانشگاه‌ها و مراکز آموزش عالی | مدرسان علوم خانواده و مدیریت مصرف در آموزش عالی | کارشناسان آموزش بهداشت و ارتقای سلامت | متخصصان انفورماتیک سلامت | مدیران خدمات درمانی و بهداشتی | مربیان و استادان پرستاری دانشگاه | متخصصان پزشکی اجتماعی و طب پیشگیری | استادان روان‌شناسی دانشگاه | مدرسان علوم ورزشی، تربیت بدنی و اوقات فراغت در آموزش عالی | مدرسان مددکاری اجتماعی در دانشگاه‌ها و مراکز آموزش عالی | معلمان آموزش استثنایی دوره ابتدایی | معلمان آموزش استثنایی دوره آمادگی و نوآموزان | دبیران آموزش استثنایی دوره دوم متوسطه | دستیاران آموزشی در آموزش عالی | کمک‌معلمان آموزش استثنایی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>سخن گفتن | راهبردهای یادگیری | نگارش | شنیدن فعال | درک مطلب | تفکر انتقادی | یادگیری فعال | نظارت</t>
+          <t>سخن گفتن | راهبردهای یادگیری | نگارش | گوش دادن فعال | درک مطلب | تفکر انتقادی | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>پزشکی و دندان‌پزشکی | آموزش و تدریس | روان‌شناسی | زبان انگلیسی | زیست‌شناسی | خدمات مشتریان و خدمات فردی | ریاضیات | درمان و مشاوره | جامعه‌شناسی و انسان‌شناسی | رایانه و الکترونیک | امور اداری و دفتری | ارتباطات و رسانه | ایمنی و امنیت عمومی | مدیریت و امور اداری</t>
+          <t>پزشکی و دندان‌پزشکی | آموزش و پرورش | روان‌شناسی | زبان انگلیسی | زیست‌شناسی | خدمات مشتری و شخصی | ریاضیات | درمان و مشاوره | جامعه‌شناسی و انسان‌شناسی | رایانه و الکترونیک | اداری | ارتباطات و رسانه | ایمنی و امنیت عمومی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | وضوح گفتار | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | دید نزدیک | تشخیص گفتار | مرتب‌سازی اطلاعات | انعطاف‌پذیری در طبقه‌بندی | روانی کلام و سیالی ایده‌ها | توجه انتخابی | تشخیص الگوها | استدلال ریاضی | ابتکار و اصالت</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | وضوح گفتار | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | بینایی نزدیک | تشخیص گفتار | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | توجه انتخابی | انعطاف‌پذیری بستار | استدلال ریاضی | اصالت</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>پرستاران بخش مراقبت‌های حاد | پرستاران پیشرفته روان‌پزشکی | متخصصان بالینی پرستاری | پرستاران بخش مراقبت‌های ویژه (ICU/CCU) | استادان علوم تربیتی دانشگاه | کارشناسان آموزش سلامت و بهداشت | متخصصان انفورماتیک سلامت | استادان تخصص‌های علوم پزشکی و بهداشت دانشگاه | بهیاران و کمک‌پرستاران دارای مجوز | مدیران خدمات درمانی و بهداشتی | ماماها | پرستاران متخصص دوره‌دیده (نرس پرکتیشنر) | استادان روان‌شناسی دانشگاه | پرستاران دارای پروانه (RN) | معلمان آموزش استثنایی دوره ابتدایی | معلمان آموزش استثنایی دوره پیش‌دبستانی | دستیاران آموزشی دانشگاه | دستیاران آموزشی مدارس (به‌جز آموزش استثنایی) | دستیاران آموزشی آموزش استثنایی | معلمان خصوصی و مدرسان تقویتی</t>
+          <t>پرستاران مراقبت‌های حاد | پرستاران تخصصی روانپزشکی | پرستاران متخصص بالینی | پرستاران مراقبت‌های ویژه | مدرسان علوم تربیتی و آموزش در دانشگاه‌ها و مراکز آموزش عالی | کارشناسان آموزش بهداشت و ارتقای سلامت | متخصصان انفورماتیک سلامت | استادان تخصص‌های علوم پزشکی و بهداشت دانشگاه | بهیاران و کمک‌پرستاران دارای مجوز | مدیران خدمات درمانی و بهداشتی | ماماهای پرستار | پرستاران بالینی پیشرفته | استادان روان‌شناسی دانشگاه | پرستاران | معلمان آموزش استثنایی دوره ابتدایی | معلمان آموزش استثنایی دوره آمادگی و نوآموزان | دستیاران آموزشی در آموزش عالی | کمک‌معلمان دوره‌های پیش‌دبستانی، ابتدایی، دوره اول و دوم متوسطه (به‌جز آموزش استثنایی) | کمک‌معلمان آموزش استثنایی | معلمان خصوصی و مدرسان تقویتی</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
